--- a/jogos_2025-06-08.xlsx
+++ b/jogos_2025-06-08.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,22 +772,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="M3" t="n">
-        <v>3.97</v>
+        <v>3.62</v>
       </c>
       <c r="N3" t="n">
-        <v>5.1</v>
+        <v>3.41</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="T3" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="Z3" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['9001']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.02</v>
+        <v>2.2</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45816.08333333334</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Central Coast II</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.21</v>
+        <v>2.31</v>
       </c>
       <c r="M4" t="n">
-        <v>6.6</v>
+        <v>3.83</v>
       </c>
       <c r="N4" t="n">
-        <v>8.300000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.21</v>
+        <v>2.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.88</v>
+        <v>1.42</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['45+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45816.08333333334</v>
@@ -1030,25 +1030,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Central Coast II</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.31</v>
+        <v>1.21</v>
       </c>
       <c r="M5" t="n">
-        <v>3.83</v>
+        <v>6.6</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.2</v>
+        <v>3.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.42</v>
+        <v>1.88</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>['45+2']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['13']</t>
-        </is>
-      </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45816.08333333334</v>
@@ -1159,16 +1159,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.16</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>3.97</v>
       </c>
       <c r="N6" t="n">
-        <v>2.06</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.62</v>
+        <v>5.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2.7</v>
       </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.82</v>
-      </c>
       <c r="AB6" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9001']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.27</v>
+        <v>1.39</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.82</v>
+        <v>3.02</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45816.08333333334</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.88</v>
+        <v>3.16</v>
       </c>
       <c r="M7" t="n">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3.41</v>
+        <v>2.06</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="V7" t="n">
         <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="X7" t="n">
-        <v>4.4</v>
+        <v>2.83</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.94</v>
+        <v>1.66</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.5</v>
+        <v>3.82</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.67</v>
+        <v>2.27</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45816.08333333334</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Gimnasia Mendoza</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,43 +2088,43 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>3.7</v>
       </c>
       <c r="M13" t="n">
-        <v>3.41</v>
+        <v>2.89</v>
       </c>
       <c r="N13" t="n">
-        <v>4.75</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="T13" t="n">
         <v>3.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="X13" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Y13" t="n">
         <v>2.65</v>
@@ -2133,20 +2133,20 @@
         <v>1.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.1</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.79</v>
+        <v>1.91</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45816.625</v>
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,43 +2217,43 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.7</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>2.89</v>
+        <v>3.41</v>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>4.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="T14" t="n">
         <v>3.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Y14" t="n">
         <v>2.65</v>
@@ -2262,38 +2262,38 @@
         <v>1.42</v>
       </c>
       <c r="AA14" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG14" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.21</v>
+        <v>2.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.91</v>
+        <v>2.79</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45816.625</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="M15" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="N15" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q15" t="n">
         <v>4.5</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.65</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="U15" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['21', '90+4']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45816.66666666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,19 +2449,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.23</v>
+        <v>1.72</v>
       </c>
       <c r="M16" t="n">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W16" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="X16" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['21', '90+4']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45816.66666666666</v>
@@ -3739,16 +3739,16 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3761,69 +3761,69 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.36</v>
+        <v>1.29</v>
       </c>
       <c r="M26" t="n">
-        <v>3.64</v>
+        <v>4.75</v>
       </c>
       <c r="N26" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
-        <v>2.53</v>
+        <v>1.62</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1.72</v>
       </c>
-      <c r="Z26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD26" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45816.875</v>
@@ -3868,16 +3868,16 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3890,87 +3890,87 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>2.36</v>
       </c>
       <c r="M27" t="n">
-        <v>4.75</v>
+        <v>3.64</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.62</v>
+        <v>2.53</v>
       </c>
       <c r="P27" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="T27" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.73</v>
       </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45816.875</v>
@@ -4023,34 +4023,34 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.13</v>
       </c>
       <c r="N28" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="O28" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
         <v>1.06</v>
@@ -4059,47 +4059,47 @@
         <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="Y28" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['40', '70', '88']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['40', '70', '88']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45816.91666666666</v>
